--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394470</v>
+        <v>122394466</v>
       </c>
       <c r="B2" t="n">
-        <v>94947</v>
+        <v>92100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammalt exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394469</v>
+        <v>122394473</v>
       </c>
       <c r="B3" t="n">
-        <v>94947</v>
+        <v>94957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,7 +832,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -835,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584355</v>
+        <v>584378</v>
       </c>
       <c r="R3" t="n">
-        <v>6538304</v>
+        <v>6538231</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394467</v>
+        <v>122394470</v>
       </c>
       <c r="B4" t="n">
-        <v>94947</v>
+        <v>94957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584280</v>
+        <v>584377</v>
       </c>
       <c r="R4" t="n">
-        <v>6538340</v>
+        <v>6538281</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394466</v>
+        <v>122394468</v>
       </c>
       <c r="B5" t="n">
-        <v>92090</v>
+        <v>94957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1052,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584377</v>
+        <v>584324</v>
       </c>
       <c r="R5" t="n">
-        <v>6538281</v>
+        <v>6538296</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammalt exemplar</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394468</v>
+        <v>122394467</v>
       </c>
       <c r="B6" t="n">
-        <v>94947</v>
+        <v>94957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584324</v>
+        <v>584280</v>
       </c>
       <c r="R6" t="n">
-        <v>6538296</v>
+        <v>6538340</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1226,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394473</v>
+        <v>122394469</v>
       </c>
       <c r="B7" t="n">
-        <v>94947</v>
+        <v>94957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,11 +1305,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1311,13 +1316,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584378</v>
+        <v>584355</v>
       </c>
       <c r="R7" t="n">
-        <v>6538231</v>
+        <v>6538304</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,12 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Riklig i området</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394466</v>
+        <v>122394467</v>
       </c>
       <c r="B2" t="n">
-        <v>92100</v>
+        <v>94957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584377</v>
+        <v>584280</v>
       </c>
       <c r="R2" t="n">
-        <v>6538281</v>
+        <v>6538340</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammalt exemplar</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394473</v>
+        <v>122394471</v>
       </c>
       <c r="B3" t="n">
         <v>94957</v>
@@ -832,11 +824,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -847,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584378</v>
+        <v>584377</v>
       </c>
       <c r="R3" t="n">
-        <v>6538231</v>
+        <v>6538281</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig i området</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394470</v>
+        <v>122394473</v>
       </c>
       <c r="B4" t="n">
         <v>94957</v>
@@ -957,7 +940,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -968,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584377</v>
+        <v>584378</v>
       </c>
       <c r="R4" t="n">
-        <v>6538281</v>
+        <v>6538231</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1000,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394468</v>
+        <v>122394469</v>
       </c>
       <c r="B5" t="n">
         <v>94957</v>
@@ -1084,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584324</v>
+        <v>584355</v>
       </c>
       <c r="R5" t="n">
-        <v>6538296</v>
+        <v>6538304</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1119,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394467</v>
+        <v>122394468</v>
       </c>
       <c r="B6" t="n">
         <v>94957</v>
@@ -1200,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584280</v>
+        <v>584324</v>
       </c>
       <c r="R6" t="n">
-        <v>6538340</v>
+        <v>6538296</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1235,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394469</v>
+        <v>122394466</v>
       </c>
       <c r="B7" t="n">
-        <v>94957</v>
+        <v>92100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,31 +1276,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1316,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584355</v>
+        <v>584377</v>
       </c>
       <c r="R7" t="n">
-        <v>6538304</v>
+        <v>6538281</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1351,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1356,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammalt exemplar</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394467</v>
+        <v>122394470</v>
       </c>
       <c r="B2" t="n">
-        <v>94957</v>
+        <v>94969</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584280</v>
+        <v>584377</v>
       </c>
       <c r="R2" t="n">
-        <v>6538340</v>
+        <v>6538281</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394471</v>
+        <v>122394469</v>
       </c>
       <c r="B3" t="n">
-        <v>94957</v>
+        <v>94969</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584377</v>
+        <v>584355</v>
       </c>
       <c r="R3" t="n">
-        <v>6538281</v>
+        <v>6538304</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394473</v>
+        <v>122394468</v>
       </c>
       <c r="B4" t="n">
-        <v>94957</v>
+        <v>94969</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,11 +940,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -955,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584378</v>
+        <v>584324</v>
       </c>
       <c r="R4" t="n">
-        <v>6538231</v>
+        <v>6538296</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,12 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Riklig i området</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394469</v>
+        <v>122394466</v>
       </c>
       <c r="B5" t="n">
-        <v>94957</v>
+        <v>92112</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,31 +1035,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1076,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584355</v>
+        <v>584377</v>
       </c>
       <c r="R5" t="n">
-        <v>6538304</v>
+        <v>6538281</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1111,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammalt exemplar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394468</v>
+        <v>122394467</v>
       </c>
       <c r="B6" t="n">
-        <v>94957</v>
+        <v>94969</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584324</v>
+        <v>584280</v>
       </c>
       <c r="R6" t="n">
-        <v>6538296</v>
+        <v>6538340</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1227,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394466</v>
+        <v>122394473</v>
       </c>
       <c r="B7" t="n">
-        <v>92100</v>
+        <v>94969</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,25 +1275,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1304,6 +1303,7 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584377</v>
+        <v>584378</v>
       </c>
       <c r="R7" t="n">
-        <v>6538281</v>
+        <v>6538231</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammalt exemplar</t>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394470</v>
+        <v>122394469</v>
       </c>
       <c r="B2" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584377</v>
+        <v>584355</v>
       </c>
       <c r="R2" t="n">
-        <v>6538281</v>
+        <v>6538304</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394469</v>
+        <v>122394467</v>
       </c>
       <c r="B3" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584355</v>
+        <v>584280</v>
       </c>
       <c r="R3" t="n">
-        <v>6538304</v>
+        <v>6538340</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
         <v>122394468</v>
       </c>
       <c r="B4" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394466</v>
+        <v>122394473</v>
       </c>
       <c r="B5" t="n">
-        <v>92112</v>
+        <v>94974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1063,6 +1063,7 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,13 +1071,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584377</v>
+        <v>584378</v>
       </c>
       <c r="R5" t="n">
-        <v>6538281</v>
+        <v>6538231</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gammalt exemplar</t>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394467</v>
+        <v>122394470</v>
       </c>
       <c r="B6" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584280</v>
+        <v>584377</v>
       </c>
       <c r="R6" t="n">
-        <v>6538340</v>
+        <v>6538281</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1226,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394473</v>
+        <v>122394466</v>
       </c>
       <c r="B7" t="n">
-        <v>94969</v>
+        <v>92117</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,25 +1276,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1303,7 +1304,6 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584378</v>
+        <v>584377</v>
       </c>
       <c r="R7" t="n">
-        <v>6538231</v>
+        <v>6538281</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Riklig i området</t>
+          <t>Gammalt exemplar</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394469</v>
+        <v>122394473</v>
       </c>
       <c r="B2" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>2180</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Leucobryum glaucum</t>
@@ -708,7 +703,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584355</v>
+        <v>584378</v>
       </c>
       <c r="R2" t="n">
-        <v>6538304</v>
+        <v>6538231</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394467</v>
+        <v>122394466</v>
       </c>
       <c r="B3" t="n">
-        <v>94974</v>
+        <v>92122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +807,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
+        <v>5966</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584280</v>
+        <v>584377</v>
       </c>
       <c r="R3" t="n">
-        <v>6538340</v>
+        <v>6538281</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammalt exemplar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394468</v>
+        <v>122394469</v>
       </c>
       <c r="B4" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,11 +931,6 @@
       </c>
       <c r="E4" t="n">
         <v>2180</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -951,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584324</v>
+        <v>584355</v>
       </c>
       <c r="R4" t="n">
-        <v>6538296</v>
+        <v>6538304</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394473</v>
+        <v>122394468</v>
       </c>
       <c r="B5" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,11 +1043,6 @@
       <c r="E5" t="n">
         <v>2180</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Leucobryum glaucum</t>
@@ -1056,11 +1053,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1071,13 +1064,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584378</v>
+        <v>584324</v>
       </c>
       <c r="R5" t="n">
-        <v>6538231</v>
+        <v>6538296</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Riklig i området</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394470</v>
+        <v>122394467</v>
       </c>
       <c r="B6" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,11 +1153,6 @@
       </c>
       <c r="E6" t="n">
         <v>2180</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1192,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584377</v>
+        <v>584280</v>
       </c>
       <c r="R6" t="n">
-        <v>6538281</v>
+        <v>6538340</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1227,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394466</v>
+        <v>122394470</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>94983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1259,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>2180</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1346,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,12 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammalt exemplar</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394473</v>
+        <v>122394468</v>
       </c>
       <c r="B2" t="n">
-        <v>94983</v>
+        <v>94996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>2180</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Leucobryum glaucum</t>
@@ -703,11 +708,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584378</v>
+        <v>584324</v>
       </c>
       <c r="R2" t="n">
-        <v>6538231</v>
+        <v>6538296</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig i området</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394466</v>
+        <v>122394471</v>
       </c>
       <c r="B3" t="n">
-        <v>92122</v>
+        <v>94996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,29 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammalt exemplar</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394469</v>
+        <v>122394466</v>
       </c>
       <c r="B4" t="n">
-        <v>94983</v>
+        <v>92135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,26 +919,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584355</v>
+        <v>584377</v>
       </c>
       <c r="R4" t="n">
-        <v>6538304</v>
+        <v>6538281</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammalt exemplar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394468</v>
+        <v>122394473</v>
       </c>
       <c r="B5" t="n">
-        <v>94983</v>
+        <v>94996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,6 +1049,11 @@
       <c r="E5" t="n">
         <v>2180</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Leucobryum glaucum</t>
@@ -1053,7 +1064,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1064,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584324</v>
+        <v>584378</v>
       </c>
       <c r="R5" t="n">
-        <v>6538296</v>
+        <v>6538231</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1124,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1159,7 @@
         <v>122394467</v>
       </c>
       <c r="B6" t="n">
-        <v>94983</v>
+        <v>94996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,6 +1173,11 @@
       </c>
       <c r="E6" t="n">
         <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1247,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394470</v>
+        <v>122394469</v>
       </c>
       <c r="B7" t="n">
-        <v>94983</v>
+        <v>94996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,6 +1289,11 @@
       </c>
       <c r="E7" t="n">
         <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1286,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584377</v>
+        <v>584355</v>
       </c>
       <c r="R7" t="n">
-        <v>6538281</v>
+        <v>6538304</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1321,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394468</v>
+        <v>122394470</v>
       </c>
       <c r="B2" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584324</v>
+        <v>584377</v>
       </c>
       <c r="R2" t="n">
-        <v>6538296</v>
+        <v>6538281</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394471</v>
+        <v>122394473</v>
       </c>
       <c r="B3" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,7 +824,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -835,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584377</v>
+        <v>584378</v>
       </c>
       <c r="R3" t="n">
-        <v>6538281</v>
+        <v>6538231</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394466</v>
+        <v>122394469</v>
       </c>
       <c r="B4" t="n">
-        <v>92135</v>
+        <v>95009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +928,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584377</v>
+        <v>584355</v>
       </c>
       <c r="R4" t="n">
-        <v>6538281</v>
+        <v>6538304</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammalt exemplar</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394473</v>
+        <v>122394467</v>
       </c>
       <c r="B5" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,11 +1065,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1079,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584378</v>
+        <v>584280</v>
       </c>
       <c r="R5" t="n">
-        <v>6538231</v>
+        <v>6538340</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,12 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Riklig i området</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394467</v>
+        <v>122394466</v>
       </c>
       <c r="B6" t="n">
-        <v>94996</v>
+        <v>92148</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,31 +1160,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584280</v>
+        <v>584377</v>
       </c>
       <c r="R6" t="n">
-        <v>6538340</v>
+        <v>6538281</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1235,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1240,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammalt exemplar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394469</v>
+        <v>122394468</v>
       </c>
       <c r="B7" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584355</v>
+        <v>584324</v>
       </c>
       <c r="R7" t="n">
-        <v>6538304</v>
+        <v>6538296</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394470</v>
+        <v>122394468</v>
       </c>
       <c r="B2" t="n">
         <v>95009</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584377</v>
+        <v>584324</v>
       </c>
       <c r="R2" t="n">
-        <v>6538281</v>
+        <v>6538296</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394473</v>
+        <v>122394471</v>
       </c>
       <c r="B3" t="n">
         <v>95009</v>
@@ -824,11 +824,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -839,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584378</v>
+        <v>584377</v>
       </c>
       <c r="R3" t="n">
-        <v>6538231</v>
+        <v>6538281</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,12 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig i området</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1272,7 +1263,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394468</v>
+        <v>122394473</v>
       </c>
       <c r="B7" t="n">
         <v>95009</v>
@@ -1305,7 +1296,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1316,13 +1311,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584324</v>
+        <v>584378</v>
       </c>
       <c r="R7" t="n">
-        <v>6538296</v>
+        <v>6538231</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1356,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394468</v>
+        <v>122394466</v>
       </c>
       <c r="B2" t="n">
-        <v>95009</v>
+        <v>92149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584324</v>
+        <v>584377</v>
       </c>
       <c r="R2" t="n">
-        <v>6538296</v>
+        <v>6538281</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammalt exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394471</v>
+        <v>122394473</v>
       </c>
       <c r="B3" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,7 +832,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -835,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584377</v>
+        <v>584378</v>
       </c>
       <c r="R3" t="n">
-        <v>6538281</v>
+        <v>6538231</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394469</v>
+        <v>122394468</v>
       </c>
       <c r="B4" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584355</v>
+        <v>584324</v>
       </c>
       <c r="R4" t="n">
-        <v>6538304</v>
+        <v>6538296</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394467</v>
+        <v>122394469</v>
       </c>
       <c r="B5" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584280</v>
+        <v>584355</v>
       </c>
       <c r="R5" t="n">
-        <v>6538340</v>
+        <v>6538304</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394466</v>
+        <v>122394471</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>95011</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,34 +1168,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,12 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammalt exemplar</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394473</v>
+        <v>122394467</v>
       </c>
       <c r="B7" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,11 +1305,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1311,13 +1316,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584378</v>
+        <v>584280</v>
       </c>
       <c r="R7" t="n">
-        <v>6538231</v>
+        <v>6538340</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,12 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Riklig i området</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1377-2025 artfynd.xlsx
+++ b/artfynd/A 1377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122394466</v>
+        <v>122394470</v>
       </c>
       <c r="B2" t="n">
-        <v>92149</v>
+        <v>95011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammalt exemplar</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122394473</v>
+        <v>122394466</v>
       </c>
       <c r="B3" t="n">
-        <v>95011</v>
+        <v>92149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +831,6 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584378</v>
+        <v>584377</v>
       </c>
       <c r="R3" t="n">
-        <v>6538231</v>
+        <v>6538281</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Riklig i området</t>
+          <t>Gammalt exemplar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1040,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394469</v>
+        <v>122394467</v>
       </c>
       <c r="B5" t="n">
         <v>95011</v>
@@ -1084,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584355</v>
+        <v>584280</v>
       </c>
       <c r="R5" t="n">
-        <v>6538304</v>
+        <v>6538340</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1119,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394471</v>
+        <v>122394473</v>
       </c>
       <c r="B6" t="n">
         <v>95011</v>
@@ -1189,7 +1180,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1200,13 +1195,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584377</v>
+        <v>584378</v>
       </c>
       <c r="R6" t="n">
-        <v>6538281</v>
+        <v>6538231</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1240,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig i området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,7 +1272,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394467</v>
+        <v>122394469</v>
       </c>
       <c r="B7" t="n">
         <v>95011</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584280</v>
+        <v>584355</v>
       </c>
       <c r="R7" t="n">
-        <v>6538340</v>
+        <v>6538304</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
